--- a/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>46.06650647039178</v>
+        <v>45.86723113598621</v>
       </c>
       <c r="M2" t="n">
-        <v>98.23139323445849</v>
+        <v>98.77846615793067</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96108470845317</v>
+        <v>88.06102662474552</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87786876670077</v>
+        <v>45.92520816376108</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228599183567575</v>
+        <v>2.228819714776162</v>
       </c>
       <c r="E3" t="n">
-        <v>5.673781308159791</v>
+        <v>5.706277742000553</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742866394522525</v>
+        <v>0.7429399049253873</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95616181262081</v>
+        <v>33.971549871877</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17185414803615</v>
+        <v>34.17523562656781</v>
       </c>
       <c r="I3" t="n">
-        <v>6.544906895780547</v>
+        <v>6.592829358814917</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642914965765781</v>
+        <v>4.64337440578367</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03891529154682</v>
+        <v>11.9389733752545</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84827349201846</v>
+        <v>48.89917915579137</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7650575502661</v>
+        <v>106.7633606948069</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.97526345088467</v>
+        <v>87.26312073337701</v>
       </c>
       <c r="C4" t="n">
-        <v>42.52460228793838</v>
+        <v>42.76735208649046</v>
       </c>
       <c r="D4" t="n">
-        <v>2.180671094125063</v>
+        <v>2.190980897509252</v>
       </c>
       <c r="E4" t="n">
-        <v>6.462680311952855</v>
+        <v>6.526998345390846</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444224485799193</v>
+        <v>0.7445023496670111</v>
       </c>
       <c r="G4" t="n">
-        <v>33.22590310460385</v>
+        <v>33.3948126600901</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24343263467628</v>
+        <v>34.2471080846825</v>
       </c>
       <c r="I4" t="n">
-        <v>5.465513553322205</v>
+        <v>5.505578710618484</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652640303624496</v>
+        <v>4.653139685418819</v>
       </c>
       <c r="K4" t="n">
-        <v>13.02473654911533</v>
+        <v>12.73687926662299</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26885819361905</v>
+        <v>44.31263449803058</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81819703067276</v>
+        <v>99.81686585114403</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.6974562480499</v>
+        <v>86.12618100077684</v>
       </c>
       <c r="C5" t="n">
-        <v>42.09496886105499</v>
+        <v>42.48501822986517</v>
       </c>
       <c r="D5" t="n">
-        <v>2.117871199297578</v>
+        <v>2.135622096336476</v>
       </c>
       <c r="E5" t="n">
-        <v>7.037011587515758</v>
+        <v>7.128106727730254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457435923291122</v>
+        <v>0.7458267009976562</v>
       </c>
       <c r="G5" t="n">
-        <v>32.2690493974406</v>
+        <v>32.55103679862381</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30420524713915</v>
+        <v>34.30802824589217</v>
       </c>
       <c r="I5" t="n">
-        <v>4.562677772270746</v>
+        <v>4.596143549961115</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660897452056951</v>
+        <v>4.66141688123535</v>
       </c>
       <c r="K5" t="n">
-        <v>14.30254375195012</v>
+        <v>13.87381899922315</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45066756606928</v>
+        <v>43.48823002895006</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84818017907438</v>
+        <v>99.84706725803838</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.27935383377925</v>
+        <v>84.73591946324777</v>
       </c>
       <c r="C6" t="n">
-        <v>41.38527860846114</v>
+        <v>41.80868405698704</v>
       </c>
       <c r="D6" t="n">
-        <v>2.048448725611762</v>
+        <v>2.067732146557483</v>
       </c>
       <c r="E6" t="n">
-        <v>7.441002474692548</v>
+        <v>7.54082566536473</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468667461115162</v>
+        <v>0.7469521253404459</v>
       </c>
       <c r="G6" t="n">
-        <v>31.21129043957617</v>
+        <v>31.51626184602165</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35587032112973</v>
+        <v>34.3597977656605</v>
       </c>
       <c r="I6" t="n">
-        <v>3.807957963460559</v>
+        <v>3.835899130925171</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667917163196975</v>
+        <v>4.668450783377786</v>
       </c>
       <c r="K6" t="n">
-        <v>15.72064616622074</v>
+        <v>15.26408053675224</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76733417608839</v>
+        <v>42.79956475209512</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87325895077028</v>
+        <v>99.8723293458344</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.62726655486922</v>
+        <v>83.19989133478479</v>
       </c>
       <c r="C7" t="n">
-        <v>40.32440415756262</v>
+        <v>40.86850742300539</v>
       </c>
       <c r="D7" t="n">
-        <v>1.967819103433505</v>
+        <v>1.993054012670902</v>
       </c>
       <c r="E7" t="n">
-        <v>7.677675857335148</v>
+        <v>7.801928443597288</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478240850137835</v>
+        <v>0.7479099615177968</v>
       </c>
       <c r="G7" t="n">
-        <v>29.98277320876906</v>
+        <v>30.37802175740081</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39990791063402</v>
+        <v>34.40385822981864</v>
       </c>
       <c r="I7" t="n">
-        <v>3.177365858347563</v>
+        <v>3.200681670293131</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673900531336145</v>
+        <v>4.674437259486229</v>
       </c>
       <c r="K7" t="n">
-        <v>17.37273344513076</v>
+        <v>16.8001086652152</v>
       </c>
       <c r="L7" t="n">
-        <v>42.1970857872105</v>
+        <v>42.22483115814259</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89422338990389</v>
+        <v>99.89344724636318</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.52924663844843</v>
+        <v>87.99782893025531</v>
       </c>
       <c r="C8" t="n">
-        <v>42.66651635486242</v>
+        <v>43.13404595188625</v>
       </c>
       <c r="D8" t="n">
-        <v>1.972026326221069</v>
+        <v>1.997289929455908</v>
       </c>
       <c r="E8" t="n">
-        <v>9.536202641724742</v>
+        <v>9.608775943905139</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494229426151096</v>
+        <v>0.7494995242388895</v>
       </c>
       <c r="G8" t="n">
-        <v>30.50008601012579</v>
+        <v>30.87015505386896</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47345536029502</v>
+        <v>34.47697811498891</v>
       </c>
       <c r="I8" t="n">
-        <v>5.614159966122269</v>
+        <v>5.610758337304428</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683893391344434</v>
+        <v>4.684372026493059</v>
       </c>
       <c r="K8" t="n">
-        <v>12.47075336155156</v>
+        <v>12.00217106974471</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67599086934032</v>
+        <v>44.67715434968954</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81326058575431</v>
+        <v>99.8133713713205</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.34696437245583</v>
+        <v>85.95486985341168</v>
       </c>
       <c r="C9" t="n">
-        <v>41.35520009443332</v>
+        <v>41.96203336591757</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8730043089787</v>
+        <v>1.904680793030396</v>
       </c>
       <c r="E9" t="n">
-        <v>9.838529933731211</v>
+        <v>9.943929551857014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507948205512831</v>
+        <v>0.7508609943761116</v>
       </c>
       <c r="G9" t="n">
-        <v>28.96857499395398</v>
+        <v>29.43878629828761</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53656174535901</v>
+        <v>34.53960574130112</v>
       </c>
       <c r="I9" t="n">
-        <v>4.68703094143614</v>
+        <v>4.684125259708721</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692467628445518</v>
+        <v>4.692881214850697</v>
       </c>
       <c r="K9" t="n">
-        <v>14.65303562754416</v>
+        <v>14.04513014658832</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83581539007468</v>
+        <v>43.83698208923565</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84405111205216</v>
+        <v>99.84414560174154</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.01785496909295</v>
+        <v>83.61616920264663</v>
       </c>
       <c r="C10" t="n">
-        <v>39.75277117349617</v>
+        <v>40.3501299395234</v>
       </c>
       <c r="D10" t="n">
-        <v>1.768540407970827</v>
+        <v>1.799591586604125</v>
       </c>
       <c r="E10" t="n">
-        <v>9.941800272249484</v>
+        <v>10.04686824704696</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519741270999867</v>
+        <v>0.7520312253960737</v>
       </c>
       <c r="G10" t="n">
-        <v>27.3528977976972</v>
+        <v>27.81452531893607</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59080984659937</v>
+        <v>34.59343636821938</v>
       </c>
       <c r="I10" t="n">
-        <v>3.91199422310116</v>
+        <v>3.909521297718558</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699838294374915</v>
+        <v>4.700195158725459</v>
       </c>
       <c r="K10" t="n">
-        <v>16.98214503090706</v>
+        <v>16.38383079735338</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13488849166798</v>
+        <v>43.13592467257575</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86980469607121</v>
+        <v>99.86988540945254</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.31991738536493</v>
+        <v>81.2223721207927</v>
       </c>
       <c r="C11" t="n">
-        <v>37.66060755227578</v>
+        <v>38.56220836525689</v>
       </c>
       <c r="D11" t="n">
-        <v>1.648625038788576</v>
+        <v>1.693238522945</v>
       </c>
       <c r="E11" t="n">
-        <v>9.811768002477812</v>
+        <v>9.996830001600982</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529928669930446</v>
+        <v>0.7530380697662722</v>
       </c>
       <c r="G11" t="n">
-        <v>25.49824249955862</v>
+        <v>26.17073013567715</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63767188168003</v>
+        <v>34.63975120924851</v>
       </c>
       <c r="I11" t="n">
-        <v>3.264411677160329</v>
+        <v>3.262296245515584</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706205418706527</v>
+        <v>4.7064879360392</v>
       </c>
       <c r="K11" t="n">
-        <v>19.68008261463505</v>
+        <v>18.77762787920729</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55064332689192</v>
+        <v>42.5515659417103</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89133349380275</v>
+        <v>99.8914021861745</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.72702717194187</v>
+        <v>78.69379837387399</v>
       </c>
       <c r="C12" t="n">
-        <v>35.57212870511169</v>
+        <v>36.53835968383672</v>
       </c>
       <c r="D12" t="n">
-        <v>1.534753678702794</v>
+        <v>1.581975499255432</v>
       </c>
       <c r="E12" t="n">
-        <v>9.587984318905079</v>
+        <v>9.793555473773829</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538723514732464</v>
+        <v>0.7539062256580741</v>
       </c>
       <c r="G12" t="n">
-        <v>23.73706607380487</v>
+        <v>24.45104650717413</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67812816776931</v>
+        <v>34.6796863802714</v>
       </c>
       <c r="I12" t="n">
-        <v>2.723520384578793</v>
+        <v>2.721714377378168</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711702196707788</v>
+        <v>4.711913910362962</v>
       </c>
       <c r="K12" t="n">
-        <v>22.27297282805813</v>
+        <v>21.30620162612603</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06422036468683</v>
+        <v>42.06481934988403</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90932189785664</v>
+        <v>99.90938065984678</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.13658097867715</v>
+        <v>76.21850438574735</v>
       </c>
       <c r="C13" t="n">
-        <v>33.40149694970164</v>
+        <v>34.48320560348181</v>
       </c>
       <c r="D13" t="n">
-        <v>1.422137428134666</v>
+        <v>1.474137469880039</v>
       </c>
       <c r="E13" t="n">
-        <v>9.26309083074459</v>
+        <v>9.504352461132219</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546321737422677</v>
+        <v>0.7546547879669397</v>
       </c>
       <c r="G13" t="n">
-        <v>21.99530163445898</v>
+        <v>22.78429966264919</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71307999214429</v>
+        <v>34.71412024647922</v>
       </c>
       <c r="I13" t="n">
-        <v>2.271887833563169</v>
+        <v>2.270347332846363</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716451085889171</v>
+        <v>4.716592424793372</v>
       </c>
       <c r="K13" t="n">
-        <v>24.86341902132288</v>
+        <v>23.78149561425264</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65943068495942</v>
+        <v>41.65969560511616</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92434665598392</v>
+        <v>99.92439682285062</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.51452360864991</v>
+        <v>83.13427148190982</v>
       </c>
       <c r="C14" t="n">
-        <v>38.05721215138837</v>
+        <v>38.78028743625057</v>
       </c>
       <c r="D14" t="n">
-        <v>1.423782249909025</v>
+        <v>1.475876540151847</v>
       </c>
       <c r="E14" t="n">
-        <v>11.82608981265171</v>
+        <v>11.89468897207808</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555049694415067</v>
+        <v>0.7555450697310537</v>
       </c>
       <c r="G14" t="n">
-        <v>24.09585149219202</v>
+        <v>24.69992675644632</v>
       </c>
       <c r="H14" t="n">
-        <v>36.82833903223224</v>
+        <v>36.6438211948179</v>
       </c>
       <c r="I14" t="n">
-        <v>2.863049993214009</v>
+        <v>2.942256262865531</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721906059009415</v>
+        <v>4.722156685819085</v>
       </c>
       <c r="K14" t="n">
-        <v>17.48547639135007</v>
+        <v>16.86572851809019</v>
       </c>
       <c r="L14" t="n">
-        <v>44.3619867085923</v>
+        <v>44.2560244019022</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90467525133074</v>
+        <v>99.90204035624296</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.58087172443416</v>
+        <v>82.30599057879087</v>
       </c>
       <c r="C15" t="n">
-        <v>37.56522247236933</v>
+        <v>38.40640313846412</v>
       </c>
       <c r="D15" t="n">
-        <v>1.38954195423258</v>
+        <v>1.44520169934394</v>
       </c>
       <c r="E15" t="n">
-        <v>11.93972005850122</v>
+        <v>12.05652085103861</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562421926405855</v>
+        <v>0.7562960670576262</v>
       </c>
       <c r="G15" t="n">
-        <v>23.51637448317531</v>
+        <v>24.18655975005498</v>
       </c>
       <c r="H15" t="n">
-        <v>36.86427619613756</v>
+        <v>36.68024445115985</v>
       </c>
       <c r="I15" t="n">
-        <v>2.388203135743248</v>
+        <v>2.454317341025693</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726513704003658</v>
+        <v>4.726850419110163</v>
       </c>
       <c r="K15" t="n">
-        <v>18.41912827556583</v>
+        <v>17.69400942120914</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93612008558667</v>
+        <v>43.8178580996916</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92047083352182</v>
+        <v>99.91827065936485</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.8673897922353</v>
+        <v>79.86849756120982</v>
       </c>
       <c r="C16" t="n">
-        <v>35.22009163631515</v>
+        <v>36.34796275838993</v>
       </c>
       <c r="D16" t="n">
-        <v>1.288293344050208</v>
+        <v>1.352887971238971</v>
       </c>
       <c r="E16" t="n">
-        <v>11.40170960542697</v>
+        <v>11.62756695082838</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568788381185675</v>
+        <v>0.7569421903730738</v>
       </c>
       <c r="G16" t="n">
-        <v>21.80286002202708</v>
+        <v>22.64161865181608</v>
       </c>
       <c r="H16" t="n">
-        <v>36.89531053271352</v>
+        <v>36.71158133388148</v>
       </c>
       <c r="I16" t="n">
-        <v>1.991844711657899</v>
+        <v>2.047011773240136</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730492738241045</v>
+        <v>4.73088868983171</v>
       </c>
       <c r="K16" t="n">
-        <v>21.13261020776472</v>
+        <v>20.13150243879016</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58095917992726</v>
+        <v>43.45235932112476</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93366102400711</v>
+        <v>99.93182451830485</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.64397025531734</v>
+        <v>81.51482955636949</v>
       </c>
       <c r="C17" t="n">
-        <v>36.51873912416305</v>
+        <v>37.5482880615926</v>
       </c>
       <c r="D17" t="n">
-        <v>1.28933953965231</v>
+        <v>1.354018335353492</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20970574036831</v>
+        <v>12.39267468078248</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757493483312087</v>
+        <v>0.7575746302401981</v>
       </c>
       <c r="G17" t="n">
-        <v>22.2918564515355</v>
+        <v>23.07539273745509</v>
       </c>
       <c r="H17" t="n">
-        <v>37.3965632200239</v>
+        <v>37.15711114597127</v>
       </c>
       <c r="I17" t="n">
-        <v>1.964677549724699</v>
+        <v>2.043216587565722</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734334270700542</v>
+        <v>4.734841439001237</v>
       </c>
       <c r="K17" t="n">
-        <v>19.35602974468265</v>
+        <v>18.48517044363052</v>
       </c>
       <c r="L17" t="n">
-        <v>44.05979501877083</v>
+        <v>43.89849113258756</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93456388761652</v>
+        <v>99.93194963781067</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.01403505274989</v>
+        <v>79.26658804373612</v>
       </c>
       <c r="C18" t="n">
-        <v>34.19133189420693</v>
+        <v>35.61519895280424</v>
       </c>
       <c r="D18" t="n">
-        <v>1.195434419950727</v>
+        <v>1.272257160577916</v>
       </c>
       <c r="E18" t="n">
-        <v>11.59351189968236</v>
+        <v>11.92833762607774</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580237555087641</v>
+        <v>0.7581174532329752</v>
       </c>
       <c r="G18" t="n">
-        <v>20.66829695919537</v>
+        <v>21.68200597941716</v>
       </c>
       <c r="H18" t="n">
-        <v>37.42274213530664</v>
+        <v>37.1837352348334</v>
       </c>
       <c r="I18" t="n">
-        <v>1.638377411176238</v>
+        <v>1.703900506890838</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737648471929774</v>
+        <v>4.738234082706095</v>
       </c>
       <c r="K18" t="n">
-        <v>21.98596494725013</v>
+        <v>20.73341195626388</v>
       </c>
       <c r="L18" t="n">
-        <v>43.7681287821617</v>
+        <v>43.59463307461061</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94542562361875</v>
+        <v>99.94324398367873</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.9607768457257</v>
+        <v>78.42740974110004</v>
       </c>
       <c r="C19" t="n">
-        <v>33.37835132299568</v>
+        <v>35.03158178489167</v>
       </c>
       <c r="D19" t="n">
-        <v>1.158026381098128</v>
+        <v>1.242123177283198</v>
       </c>
       <c r="E19" t="n">
-        <v>11.46022008886684</v>
+        <v>11.88367291375356</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758475841318604</v>
+        <v>0.758577313742593</v>
       </c>
       <c r="G19" t="n">
-        <v>20.02153587990631</v>
+        <v>21.16845791207286</v>
       </c>
       <c r="H19" t="n">
-        <v>37.44506108053985</v>
+        <v>37.20629022464621</v>
       </c>
       <c r="I19" t="n">
-        <v>1.376983565754702</v>
+        <v>1.42717998871042</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740474008241274</v>
+        <v>4.741108210891205</v>
       </c>
       <c r="K19" t="n">
-        <v>23.03922315427428</v>
+        <v>21.57259025889997</v>
       </c>
       <c r="L19" t="n">
-        <v>43.53655342868188</v>
+        <v>43.34828412915454</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95412790595185</v>
+        <v>99.95245617294617</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.20907547540051</v>
+        <v>75.96197618385614</v>
       </c>
       <c r="C20" t="n">
-        <v>30.83780453833059</v>
+        <v>32.78561720248477</v>
       </c>
       <c r="D20" t="n">
-        <v>1.060945649338964</v>
+        <v>1.153428194876125</v>
       </c>
       <c r="E20" t="n">
-        <v>10.69082272991042</v>
+        <v>11.23343093524264</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588669837161242</v>
+        <v>0.7589734153057638</v>
       </c>
       <c r="G20" t="n">
-        <v>18.34307208504828</v>
+        <v>19.65690411738177</v>
       </c>
       <c r="H20" t="n">
-        <v>37.46437132111504</v>
+        <v>37.22571800010269</v>
       </c>
       <c r="I20" t="n">
-        <v>1.148078058045891</v>
+        <v>1.189937675286129</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742918648225776</v>
+        <v>4.743583845661023</v>
       </c>
       <c r="K20" t="n">
-        <v>25.7909245245995</v>
+        <v>24.03802381614386</v>
       </c>
       <c r="L20" t="n">
-        <v>43.33302139357671</v>
+        <v>43.1367150927961</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96175045650679</v>
+        <v>99.96035611142474</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.57193942625676</v>
+        <v>81.68438720236996</v>
       </c>
       <c r="C21" t="n">
-        <v>34.85919399911772</v>
+        <v>36.35708858026565</v>
       </c>
       <c r="D21" t="n">
-        <v>1.061640392953274</v>
+        <v>1.154211957051035</v>
       </c>
       <c r="E21" t="n">
-        <v>12.83378136431722</v>
+        <v>13.1582104073398</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593639158552739</v>
+        <v>0.7594891428190337</v>
       </c>
       <c r="G21" t="n">
-        <v>20.22723532230979</v>
+        <v>21.3098819579768</v>
       </c>
       <c r="H21" t="n">
-        <v>39.36105584120554</v>
+        <v>38.89063396726726</v>
       </c>
       <c r="I21" t="n">
-        <v>1.582838115520194</v>
+        <v>1.665152627297075</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746024474095461</v>
+        <v>4.74680714261896</v>
       </c>
       <c r="K21" t="n">
-        <v>19.42806057374323</v>
+        <v>18.31561279763005</v>
       </c>
       <c r="L21" t="n">
-        <v>45.66001868390232</v>
+        <v>45.27183122499513</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94727325676328</v>
+        <v>99.94453260289083</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.86723113598621</v>
+        <v>45.61068227315344</v>
       </c>
       <c r="M2" t="n">
-        <v>98.77846615793067</v>
+        <v>99.58378528395022</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06102662474552</v>
+        <v>87.98064112272178</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92520816376108</v>
+        <v>45.88646253613605</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228819714776162</v>
+        <v>2.228642880628946</v>
       </c>
       <c r="E3" t="n">
-        <v>5.706277742000553</v>
+        <v>5.679759987203638</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429399049253873</v>
+        <v>0.7428809602096488</v>
       </c>
       <c r="G3" t="n">
-        <v>33.971549871877</v>
+        <v>33.9589403587938</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17523562656781</v>
+        <v>34.17252416964384</v>
       </c>
       <c r="I3" t="n">
-        <v>6.592829358814917</v>
+        <v>6.554886764931608</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64337440578367</v>
+        <v>4.643006001310304</v>
       </c>
       <c r="K3" t="n">
-        <v>11.9389733752545</v>
+        <v>12.01935887727823</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89917915579137</v>
+        <v>48.85888250314747</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7633606948069</v>
+        <v>106.7647039165617</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.26312073337701</v>
+        <v>87.05340891988297</v>
       </c>
       <c r="C4" t="n">
-        <v>42.76735208649046</v>
+        <v>42.59339292357108</v>
       </c>
       <c r="D4" t="n">
-        <v>2.190980897509252</v>
+        <v>2.183853060507976</v>
       </c>
       <c r="E4" t="n">
-        <v>6.526998345390846</v>
+        <v>6.477920970070929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445023496670111</v>
+        <v>0.7444380205977845</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3948126600901</v>
+        <v>33.27645558593514</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2471080846825</v>
+        <v>34.24414894749808</v>
       </c>
       <c r="I4" t="n">
-        <v>5.505578710618484</v>
+        <v>5.473854706536918</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653139685418819</v>
+        <v>4.652737628736153</v>
       </c>
       <c r="K4" t="n">
-        <v>12.73687926662299</v>
+        <v>12.94659108011701</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31263449803058</v>
+        <v>44.27793580839715</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81686585114403</v>
+        <v>99.81791981208525</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12618100077684</v>
+        <v>85.94964867559294</v>
       </c>
       <c r="C5" t="n">
-        <v>42.48501822986517</v>
+        <v>42.33916499095191</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135622096336476</v>
+        <v>2.130145248074131</v>
       </c>
       <c r="E5" t="n">
-        <v>7.128106727730254</v>
+        <v>7.080213463561103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458267009976562</v>
+        <v>0.7457573224902783</v>
       </c>
       <c r="G5" t="n">
-        <v>32.55103679862381</v>
+        <v>32.45808292735669</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30802824589217</v>
+        <v>34.30483683455279</v>
       </c>
       <c r="I5" t="n">
-        <v>4.596143549961115</v>
+        <v>4.569629613993694</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66141688123535</v>
+        <v>4.660983265564239</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87381899922315</v>
+        <v>14.05035132440706</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48823002895006</v>
+        <v>43.458432165015</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84706725803838</v>
+        <v>99.84794848037397</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.73591946324777</v>
+        <v>84.66394386345745</v>
       </c>
       <c r="C6" t="n">
-        <v>41.80868405698704</v>
+        <v>41.76316492906805</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067732146557483</v>
+        <v>2.067518105057095</v>
       </c>
       <c r="E6" t="n">
-        <v>7.54082566536473</v>
+        <v>7.507676038638565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469521253404459</v>
+        <v>0.746877093305417</v>
       </c>
       <c r="G6" t="n">
-        <v>31.51626184602165</v>
+        <v>31.50380199116786</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3597977656605</v>
+        <v>34.35634629204917</v>
       </c>
       <c r="I6" t="n">
-        <v>3.835899130925171</v>
+        <v>3.813742510080478</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668450783377786</v>
+        <v>4.667981833158856</v>
       </c>
       <c r="K6" t="n">
-        <v>15.26408053675224</v>
+        <v>15.33605613654255</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79956475209512</v>
+        <v>42.77384477844512</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8723293458344</v>
+        <v>99.87306584405572</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.19989133478479</v>
+        <v>83.22985893467572</v>
       </c>
       <c r="C7" t="n">
-        <v>40.86850742300539</v>
+        <v>40.92147475912061</v>
       </c>
       <c r="D7" t="n">
-        <v>1.993054012670902</v>
+        <v>1.997883145188748</v>
       </c>
       <c r="E7" t="n">
-        <v>7.801928443597288</v>
+        <v>7.785175578348184</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479099615177968</v>
+        <v>0.7478289509069129</v>
       </c>
       <c r="G7" t="n">
-        <v>30.37802175740081</v>
+        <v>30.44273946311095</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40385822981864</v>
+        <v>34.40013174171798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.200681670293131</v>
+        <v>3.182169112234725</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674437259486229</v>
+        <v>4.673930943168205</v>
       </c>
       <c r="K7" t="n">
-        <v>16.8001086652152</v>
+        <v>16.77014106532429</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22483115814259</v>
+        <v>42.20244688360843</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89344724636318</v>
+        <v>99.89406270805333</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.99782893025531</v>
+        <v>88.1757041329089</v>
       </c>
       <c r="C8" t="n">
-        <v>43.13404595188625</v>
+        <v>43.22960754514048</v>
       </c>
       <c r="D8" t="n">
-        <v>1.997289929455908</v>
+        <v>2.002184269244967</v>
       </c>
       <c r="E8" t="n">
-        <v>9.608775943905139</v>
+        <v>9.62554100431343</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494995242388895</v>
+        <v>0.7494389074744073</v>
       </c>
       <c r="G8" t="n">
-        <v>30.87015505386896</v>
+        <v>30.94550982067252</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47697811498891</v>
+        <v>34.47418974382273</v>
       </c>
       <c r="I8" t="n">
-        <v>5.610758337304428</v>
+        <v>5.694847215665813</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684372026493059</v>
+        <v>4.683993171715046</v>
       </c>
       <c r="K8" t="n">
-        <v>12.00217106974471</v>
+        <v>11.8242958670911</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67715434968954</v>
+        <v>44.75667613928834</v>
       </c>
       <c r="M8" t="n">
-        <v>99.8133713713205</v>
+        <v>99.81057955151992</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.95486985341168</v>
+        <v>86.30328760997455</v>
       </c>
       <c r="C9" t="n">
-        <v>41.96203336591757</v>
+        <v>42.24120848094677</v>
       </c>
       <c r="D9" t="n">
-        <v>1.904680793030396</v>
+        <v>1.917641011696702</v>
       </c>
       <c r="E9" t="n">
-        <v>9.943929551857014</v>
+        <v>10.01150104262304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508609943761116</v>
+        <v>0.7508151191748095</v>
       </c>
       <c r="G9" t="n">
-        <v>29.43878629828761</v>
+        <v>29.63881979872059</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53960574130112</v>
+        <v>34.53749548204123</v>
       </c>
       <c r="I9" t="n">
-        <v>4.684125259708721</v>
+        <v>4.754420660875631</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692881214850697</v>
+        <v>4.69259449484256</v>
       </c>
       <c r="K9" t="n">
-        <v>14.04513014658832</v>
+        <v>13.69671239002546</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83698208923565</v>
+        <v>43.90388892859261</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84414560174154</v>
+        <v>99.84180979956483</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.61616920264663</v>
+        <v>84.30193172156697</v>
       </c>
       <c r="C10" t="n">
-        <v>40.3501299395234</v>
+        <v>40.97775728670695</v>
       </c>
       <c r="D10" t="n">
-        <v>1.799591586604125</v>
+        <v>1.828177142313072</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04686824704696</v>
+        <v>10.20580593957471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520312253960737</v>
+        <v>0.7519931902289392</v>
       </c>
       <c r="G10" t="n">
-        <v>27.81452531893607</v>
+        <v>28.25607741524832</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59343636821938</v>
+        <v>34.5916867505312</v>
       </c>
       <c r="I10" t="n">
-        <v>3.909521297718558</v>
+        <v>3.968233844739863</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700195158725459</v>
+        <v>4.69995743893087</v>
       </c>
       <c r="K10" t="n">
-        <v>16.38383079735338</v>
+        <v>15.69806827843304</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13592467257575</v>
+        <v>43.19210719428015</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86988540945254</v>
+        <v>99.86793275942013</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.2223721207927</v>
+        <v>81.98918931721927</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56220836525689</v>
+        <v>39.28045487256455</v>
       </c>
       <c r="D11" t="n">
-        <v>1.693238522945</v>
+        <v>1.725555445869393</v>
       </c>
       <c r="E11" t="n">
-        <v>9.996830001600982</v>
+        <v>10.18480548485142</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530380697662722</v>
+        <v>0.7530055534127026</v>
       </c>
       <c r="G11" t="n">
-        <v>26.17073013567715</v>
+        <v>26.66996930127861</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63975120924851</v>
+        <v>34.63825545698431</v>
       </c>
       <c r="I11" t="n">
-        <v>3.262296245515584</v>
+        <v>3.311313365993436</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7064879360392</v>
+        <v>4.706284708829391</v>
       </c>
       <c r="K11" t="n">
-        <v>18.77762787920729</v>
+        <v>18.01081068278074</v>
       </c>
       <c r="L11" t="n">
-        <v>42.5515659417103</v>
+        <v>42.59850572674529</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8914021861745</v>
+        <v>99.88977128209058</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.69379837387399</v>
+        <v>79.51878732135521</v>
       </c>
       <c r="C12" t="n">
-        <v>36.53835968383672</v>
+        <v>37.32283842371383</v>
       </c>
       <c r="D12" t="n">
-        <v>1.581975499255432</v>
+        <v>1.616933842487538</v>
       </c>
       <c r="E12" t="n">
-        <v>9.793555473773829</v>
+        <v>10.00412167579038</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539062256580741</v>
+        <v>0.7538775782599484</v>
       </c>
       <c r="G12" t="n">
-        <v>24.45104650717413</v>
+        <v>24.99112737557616</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6796863802714</v>
+        <v>34.67836859995762</v>
       </c>
       <c r="I12" t="n">
-        <v>2.721714377378168</v>
+        <v>2.762623385158887</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711913910362962</v>
+        <v>4.711734864124677</v>
       </c>
       <c r="K12" t="n">
-        <v>21.30620162612603</v>
+        <v>20.48121267864479</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06481934988403</v>
+        <v>42.10396797080823</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90938065984678</v>
+        <v>99.90801907316686</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.21850438574735</v>
+        <v>77.02013904721753</v>
       </c>
       <c r="C13" t="n">
-        <v>34.48320560348181</v>
+        <v>35.25110989035952</v>
       </c>
       <c r="D13" t="n">
-        <v>1.474137469880039</v>
+        <v>1.508086583034429</v>
       </c>
       <c r="E13" t="n">
-        <v>9.504352461132219</v>
+        <v>9.714753823346379</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546547879669397</v>
+        <v>0.7546294584445116</v>
       </c>
       <c r="G13" t="n">
-        <v>22.78429966264919</v>
+        <v>23.30879773784022</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71412024647922</v>
+        <v>34.71295508844752</v>
       </c>
       <c r="I13" t="n">
-        <v>2.270347332846363</v>
+        <v>2.304482240826263</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716592424793372</v>
+        <v>4.716434115278197</v>
       </c>
       <c r="K13" t="n">
-        <v>23.78149561425264</v>
+        <v>22.97986095278248</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65969560511616</v>
+        <v>41.69228961838137</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92439682285062</v>
+        <v>99.92326046152336</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.13427148190982</v>
+        <v>83.61904868078985</v>
       </c>
       <c r="C14" t="n">
-        <v>38.78028743625057</v>
+        <v>39.34581193513872</v>
       </c>
       <c r="D14" t="n">
-        <v>1.475876540151847</v>
+        <v>1.509869475085427</v>
       </c>
       <c r="E14" t="n">
-        <v>11.89468897207808</v>
+        <v>12.00555116510702</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555450697310537</v>
+        <v>0.7555215974490258</v>
       </c>
       <c r="G14" t="n">
-        <v>24.69992675644632</v>
+        <v>25.12138515365764</v>
       </c>
       <c r="H14" t="n">
-        <v>36.6438211948179</v>
+        <v>36.53902474176872</v>
       </c>
       <c r="I14" t="n">
-        <v>2.942256262865531</v>
+        <v>2.965686563665594</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722156685819085</v>
+        <v>4.722009984056411</v>
       </c>
       <c r="K14" t="n">
-        <v>16.86572851809019</v>
+        <v>16.38095131921015</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2560244019022</v>
+        <v>44.17449725878485</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90204035624296</v>
+        <v>99.90126051313372</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.30599057879087</v>
+        <v>82.72870168780841</v>
       </c>
       <c r="C15" t="n">
-        <v>38.40640313846412</v>
+        <v>38.912591947953</v>
       </c>
       <c r="D15" t="n">
-        <v>1.44520169934394</v>
+        <v>1.476395041880268</v>
       </c>
       <c r="E15" t="n">
-        <v>12.05652085103861</v>
+        <v>12.1529852440322</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562960670576262</v>
+        <v>0.7562746861021423</v>
       </c>
       <c r="G15" t="n">
-        <v>24.18655975005498</v>
+        <v>24.56572426085295</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68024445115985</v>
+        <v>36.57673675007607</v>
       </c>
       <c r="I15" t="n">
-        <v>2.454317341025693</v>
+        <v>2.473868916726393</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726850419110163</v>
+        <v>4.72671678813839</v>
       </c>
       <c r="K15" t="n">
-        <v>17.69400942120914</v>
+        <v>17.27129831219159</v>
       </c>
       <c r="L15" t="n">
-        <v>43.8178580996916</v>
+        <v>43.73372955753137</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91827065936485</v>
+        <v>99.91761981767596</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.86849756120982</v>
+        <v>80.21658602722758</v>
       </c>
       <c r="C16" t="n">
-        <v>36.34796275838993</v>
+        <v>36.78285647738762</v>
       </c>
       <c r="D16" t="n">
-        <v>1.352887971238971</v>
+        <v>1.380474227594904</v>
       </c>
       <c r="E16" t="n">
-        <v>11.62756695082838</v>
+        <v>11.7072979985476</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569421903730738</v>
+        <v>0.7569231141258236</v>
       </c>
       <c r="G16" t="n">
-        <v>22.64161865181608</v>
+        <v>22.9696986662331</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71158133388148</v>
+        <v>36.60809755265139</v>
       </c>
       <c r="I16" t="n">
-        <v>2.047011773240136</v>
+        <v>2.063325004788358</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73088868983171</v>
+        <v>4.730769463286398</v>
       </c>
       <c r="K16" t="n">
-        <v>20.13150243879016</v>
+        <v>19.78341397277241</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45235932112476</v>
+        <v>43.36501096881979</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93182451830485</v>
+        <v>99.93128141897982</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.51482955636949</v>
+        <v>81.91042479379576</v>
       </c>
       <c r="C17" t="n">
-        <v>37.5482880615926</v>
+        <v>38.01592442280618</v>
       </c>
       <c r="D17" t="n">
-        <v>1.354018335353492</v>
+        <v>1.381631206833945</v>
       </c>
       <c r="E17" t="n">
-        <v>12.39267468078248</v>
+        <v>12.49000200783871</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575746302401981</v>
+        <v>0.7575574934652478</v>
       </c>
       <c r="G17" t="n">
-        <v>23.07539273745509</v>
+        <v>23.41859496526675</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15711114597127</v>
+        <v>37.06842423122414</v>
       </c>
       <c r="I17" t="n">
-        <v>2.043216587565722</v>
+        <v>2.059480555009154</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734841439001237</v>
+        <v>4.7347343341578</v>
       </c>
       <c r="K17" t="n">
-        <v>18.48517044363052</v>
+        <v>18.08957520620426</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89849113258756</v>
+        <v>43.82590850618606</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93194963781067</v>
+        <v>99.93140813519649</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.26658804373612</v>
+        <v>79.4352032119405</v>
       </c>
       <c r="C18" t="n">
-        <v>35.61519895280424</v>
+        <v>35.85860305752292</v>
       </c>
       <c r="D18" t="n">
-        <v>1.272257160577916</v>
+        <v>1.290852020107901</v>
       </c>
       <c r="E18" t="n">
-        <v>11.92833762607774</v>
+        <v>11.95559960160468</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581174532329752</v>
+        <v>0.7581034658369437</v>
       </c>
       <c r="G18" t="n">
-        <v>21.68200597941716</v>
+        <v>21.87989129767578</v>
       </c>
       <c r="H18" t="n">
-        <v>37.1837352348334</v>
+        <v>37.09513947814219</v>
       </c>
       <c r="I18" t="n">
-        <v>1.703900506890838</v>
+        <v>1.717470687092098</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738234082706095</v>
+        <v>4.738146661480899</v>
       </c>
       <c r="K18" t="n">
-        <v>20.73341195626388</v>
+        <v>20.56479678805949</v>
       </c>
       <c r="L18" t="n">
-        <v>43.59463307461061</v>
+        <v>43.5193923612229</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94324398367873</v>
+        <v>99.94279220680532</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.42740974110004</v>
+        <v>78.42094984120607</v>
       </c>
       <c r="C19" t="n">
-        <v>35.03158178489167</v>
+        <v>35.10873060992033</v>
       </c>
       <c r="D19" t="n">
-        <v>1.242123177283198</v>
+        <v>1.254342476351029</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88367291375356</v>
+        <v>11.85613869348987</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758577313742593</v>
+        <v>0.7585649401168625</v>
       </c>
       <c r="G19" t="n">
-        <v>21.16845791207286</v>
+        <v>21.26105595769518</v>
       </c>
       <c r="H19" t="n">
-        <v>37.20629022464621</v>
+        <v>37.1177201067115</v>
       </c>
       <c r="I19" t="n">
-        <v>1.42717998871042</v>
+        <v>1.432096791111249</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741108210891205</v>
+        <v>4.741030875730392</v>
       </c>
       <c r="K19" t="n">
-        <v>21.57259025889997</v>
+        <v>21.57905015879392</v>
       </c>
       <c r="L19" t="n">
-        <v>43.34828412915454</v>
+        <v>43.26451171219984</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95245617294617</v>
+        <v>99.9522924809141</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.96197618385614</v>
+        <v>75.72148726622383</v>
       </c>
       <c r="C20" t="n">
-        <v>32.78561720248477</v>
+        <v>32.62954182476948</v>
       </c>
       <c r="D20" t="n">
-        <v>1.153428194876125</v>
+        <v>1.156436799843527</v>
       </c>
       <c r="E20" t="n">
-        <v>11.23343093524264</v>
+        <v>11.12973381364098</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589734153057638</v>
+        <v>0.7589636635125617</v>
       </c>
       <c r="G20" t="n">
-        <v>19.65690411738177</v>
+        <v>19.60155856679324</v>
       </c>
       <c r="H20" t="n">
-        <v>37.22571800010269</v>
+        <v>37.13723024041116</v>
       </c>
       <c r="I20" t="n">
-        <v>1.189937675286129</v>
+        <v>1.194041285068851</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743583845661023</v>
+        <v>4.743522896953512</v>
       </c>
       <c r="K20" t="n">
-        <v>24.03802381614386</v>
+        <v>24.27851273377616</v>
       </c>
       <c r="L20" t="n">
-        <v>43.1367150927961</v>
+        <v>43.0521649750346</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96035611142474</v>
+        <v>99.96021953358023</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.68438720236996</v>
+        <v>81.73496684409272</v>
       </c>
       <c r="C21" t="n">
-        <v>36.35708858026565</v>
+        <v>36.36427121210784</v>
       </c>
       <c r="D21" t="n">
-        <v>1.154211957051035</v>
+        <v>1.15724714146812</v>
       </c>
       <c r="E21" t="n">
-        <v>13.1582104073398</v>
+        <v>13.14080823759601</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594891428190337</v>
+        <v>0.7594954866508268</v>
       </c>
       <c r="G21" t="n">
-        <v>21.3098819579768</v>
+        <v>21.33220162009081</v>
       </c>
       <c r="H21" t="n">
-        <v>38.89063396726726</v>
+        <v>38.88016093854522</v>
       </c>
       <c r="I21" t="n">
-        <v>1.665152627297075</v>
+        <v>1.718206628174079</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74680714261896</v>
+        <v>4.746846791567669</v>
       </c>
       <c r="K21" t="n">
-        <v>18.31561279763005</v>
+        <v>18.26503315590725</v>
       </c>
       <c r="L21" t="n">
-        <v>45.27183122499513</v>
+        <v>45.31346218249503</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94453260289083</v>
+        <v>99.94276655051013</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_52_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.61068227315344</v>
+        <v>43.62436212674547</v>
       </c>
       <c r="M2" t="n">
-        <v>99.58378528395022</v>
+        <v>96.58747412876846</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98064112272178</v>
+        <v>81.51730906428672</v>
       </c>
       <c r="C3" t="n">
-        <v>45.88646253613605</v>
+        <v>43.27286461984229</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228642880628946</v>
+        <v>2.181981871286058</v>
       </c>
       <c r="E3" t="n">
-        <v>5.679759987203638</v>
+        <v>4.160619624359592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428809602096488</v>
+        <v>0.7376614848426117</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9589403587938</v>
+        <v>32.82064398059446</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17252416964384</v>
+        <v>33.93242830276014</v>
       </c>
       <c r="I3" t="n">
-        <v>6.554886764931608</v>
+        <v>3.073589520177549</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643006001310304</v>
+        <v>4.610384280266323</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01935887727823</v>
+        <v>18.48269093571326</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85888250314747</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7647039165617</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05340891988297</v>
+        <v>88.6107239377798</v>
       </c>
       <c r="C4" t="n">
-        <v>42.59339292357108</v>
+        <v>42.79667464920955</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183853060507976</v>
+        <v>2.187772991239961</v>
       </c>
       <c r="E4" t="n">
-        <v>6.477920970070929</v>
+        <v>6.499261919397931</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444380205977845</v>
+        <v>0.7396192857759347</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27645558593514</v>
+        <v>33.48360557455278</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24414894749808</v>
+        <v>34.02248714569299</v>
       </c>
       <c r="I4" t="n">
-        <v>5.473854706536918</v>
+        <v>7.055356485020614</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652737628736153</v>
+        <v>4.622620536099592</v>
       </c>
       <c r="K4" t="n">
-        <v>12.94659108011701</v>
+        <v>11.3892760622202</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27793580839715</v>
+        <v>45.57949326581078</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81791981208525</v>
+        <v>99.76544397724052</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94964867559294</v>
+        <v>87.6405330855149</v>
       </c>
       <c r="C5" t="n">
-        <v>42.33916499095191</v>
+        <v>42.91997954162124</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130145248074131</v>
+        <v>2.142230871915225</v>
       </c>
       <c r="E5" t="n">
-        <v>7.080213463561103</v>
+        <v>7.34607582939577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457573224902783</v>
+        <v>0.7412769323350024</v>
       </c>
       <c r="G5" t="n">
-        <v>32.45808292735669</v>
+        <v>32.78658885179198</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30483683455279</v>
+        <v>34.09873888741011</v>
       </c>
       <c r="I5" t="n">
-        <v>4.569629613993694</v>
+        <v>5.892640885573065</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660983265564239</v>
+        <v>4.632980827093765</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05035132440706</v>
+        <v>12.3594669144851</v>
       </c>
       <c r="L5" t="n">
-        <v>43.458432165015</v>
+        <v>44.52457141930976</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84794848037397</v>
+        <v>99.80401787541609</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.66394386345745</v>
+        <v>86.39208540342955</v>
       </c>
       <c r="C6" t="n">
-        <v>41.76316492906805</v>
+        <v>42.5861471485711</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067518105057095</v>
+        <v>2.082913679765585</v>
       </c>
       <c r="E6" t="n">
-        <v>7.507676038638565</v>
+        <v>7.962642967269601</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746877093305417</v>
+        <v>0.7426840733670611</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50380199116786</v>
+        <v>31.87874627686249</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35634629204917</v>
+        <v>34.16346737488481</v>
       </c>
       <c r="I6" t="n">
-        <v>3.813742510080478</v>
+        <v>4.919855572735865</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667981833158856</v>
+        <v>4.641775458544132</v>
       </c>
       <c r="K6" t="n">
-        <v>15.33605613654255</v>
+        <v>13.60791459657046</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77384477844512</v>
+        <v>43.64225378581476</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87306584405572</v>
+        <v>99.83631553095631</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.22985893467572</v>
+        <v>84.888209949063</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92147475912061</v>
+        <v>41.84642481688928</v>
       </c>
       <c r="D7" t="n">
-        <v>1.997883145188748</v>
+        <v>2.011435283069988</v>
       </c>
       <c r="E7" t="n">
-        <v>7.785175578348184</v>
+        <v>8.373807711079303</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478289509069129</v>
+        <v>0.7438816583125052</v>
       </c>
       <c r="G7" t="n">
-        <v>30.44273946311095</v>
+        <v>30.78477791193615</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40013174171798</v>
+        <v>34.21855628237524</v>
       </c>
       <c r="I7" t="n">
-        <v>3.182169112234725</v>
+        <v>4.10649073783667</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673930943168205</v>
+        <v>4.649260364453157</v>
       </c>
       <c r="K7" t="n">
-        <v>16.77014106532429</v>
+        <v>15.111790050937</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20244688360843</v>
+        <v>42.9051224773755</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89406270805333</v>
+        <v>99.86333734520178</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.1757041329089</v>
+        <v>83.2117998495999</v>
       </c>
       <c r="C8" t="n">
-        <v>43.22960754514048</v>
+        <v>40.80783840074549</v>
       </c>
       <c r="D8" t="n">
-        <v>2.002184269244967</v>
+        <v>1.932179947241192</v>
       </c>
       <c r="E8" t="n">
-        <v>9.62554100431343</v>
+        <v>8.614988620087669</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494389074744073</v>
+        <v>0.7449027930105538</v>
       </c>
       <c r="G8" t="n">
-        <v>30.94550982067252</v>
+        <v>29.57178441800602</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47418974382273</v>
+        <v>34.26552847848548</v>
       </c>
       <c r="I8" t="n">
-        <v>5.694847215665813</v>
+        <v>3.426773136453026</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683993171715046</v>
+        <v>4.655642456315961</v>
       </c>
       <c r="K8" t="n">
-        <v>11.8242958670911</v>
+        <v>16.7882001504001</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75667613928834</v>
+        <v>42.28989226169229</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81057955151992</v>
+        <v>99.88593081283788</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.30328760997455</v>
+        <v>81.38329337151715</v>
       </c>
       <c r="C9" t="n">
-        <v>42.24120848094677</v>
+        <v>39.51129001365892</v>
       </c>
       <c r="D9" t="n">
-        <v>1.917641011696702</v>
+        <v>1.846276198529709</v>
       </c>
       <c r="E9" t="n">
-        <v>10.01150104262304</v>
+        <v>8.70846859737086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508151191748095</v>
+        <v>0.7457750720868549</v>
       </c>
       <c r="G9" t="n">
-        <v>29.63881979872059</v>
+        <v>28.25703775519044</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53749548204123</v>
+        <v>34.30565331599533</v>
       </c>
       <c r="I9" t="n">
-        <v>4.754420660875631</v>
+        <v>2.858988231801123</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69259449484256</v>
+        <v>4.661094200542843</v>
       </c>
       <c r="K9" t="n">
-        <v>13.69671239002546</v>
+        <v>18.61670662848287</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90388892859261</v>
+        <v>41.77681521517896</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84180979956483</v>
+        <v>99.90481185732074</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.30193172156697</v>
+        <v>85.88216367114258</v>
       </c>
       <c r="C10" t="n">
-        <v>40.97775728670695</v>
+        <v>42.68048930318163</v>
       </c>
       <c r="D10" t="n">
-        <v>1.828177142313072</v>
+        <v>1.84829501718992</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20580593957471</v>
+        <v>10.51593469569789</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519931902289392</v>
+        <v>0.7465905430510846</v>
       </c>
       <c r="G10" t="n">
-        <v>28.25607741524832</v>
+        <v>29.61633821207345</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5916867505312</v>
+        <v>35.67156765761147</v>
       </c>
       <c r="I10" t="n">
-        <v>3.968233844739863</v>
+        <v>2.817246651449474</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69995743893087</v>
+        <v>4.666190894069278</v>
       </c>
       <c r="K10" t="n">
-        <v>15.69806827843304</v>
+        <v>14.11783632885745</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19210719428015</v>
+        <v>43.10786871843739</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86793275942013</v>
+        <v>99.90619435047647</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.98918931721927</v>
+        <v>85.57730155654279</v>
       </c>
       <c r="C11" t="n">
-        <v>39.28045487256455</v>
+        <v>42.72612134361782</v>
       </c>
       <c r="D11" t="n">
-        <v>1.725555445869393</v>
+        <v>1.831125181165858</v>
       </c>
       <c r="E11" t="n">
-        <v>10.18480548485142</v>
+        <v>10.83441237962341</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530055534127026</v>
+        <v>0.7472950621724656</v>
       </c>
       <c r="G11" t="n">
-        <v>26.66996930127861</v>
+        <v>29.35360716528305</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63825545698431</v>
+        <v>35.71762060329068</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311313365993436</v>
+        <v>2.422647026429432</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706284708829391</v>
+        <v>4.67059413857791</v>
       </c>
       <c r="K11" t="n">
-        <v>18.01081068278074</v>
+        <v>14.42269844345721</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59850572674529</v>
+        <v>42.77050144445099</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88977128209058</v>
+        <v>99.91932123152601</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.51878732135521</v>
+        <v>83.62172885202244</v>
       </c>
       <c r="C12" t="n">
-        <v>37.32283842371383</v>
+        <v>41.14734583739519</v>
       </c>
       <c r="D12" t="n">
-        <v>1.616933842487538</v>
+        <v>1.747310713388411</v>
       </c>
       <c r="E12" t="n">
-        <v>10.00412167579038</v>
+        <v>10.67524819513683</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538775782599484</v>
+        <v>0.7478969426516</v>
       </c>
       <c r="G12" t="n">
-        <v>24.99112737557616</v>
+        <v>28.01003055609676</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67836859995762</v>
+        <v>35.74638800681099</v>
       </c>
       <c r="I12" t="n">
-        <v>2.762623385158887</v>
+        <v>2.020498546365348</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711734864124677</v>
+        <v>4.6743558915725</v>
       </c>
       <c r="K12" t="n">
-        <v>20.48121267864479</v>
+        <v>16.37827114797756</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10396797080823</v>
+        <v>42.40708726389312</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90801907316686</v>
+        <v>99.93270424926587</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.02013904721753</v>
+        <v>84.62910998882717</v>
       </c>
       <c r="C13" t="n">
-        <v>35.25110989035952</v>
+        <v>42.02754636039145</v>
       </c>
       <c r="D13" t="n">
-        <v>1.508086583034429</v>
+        <v>1.748584701623845</v>
       </c>
       <c r="E13" t="n">
-        <v>9.714753823346379</v>
+        <v>11.26113105884817</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546294584445116</v>
+        <v>0.7484422445827075</v>
       </c>
       <c r="G13" t="n">
-        <v>23.30879773784022</v>
+        <v>28.30003121651594</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71295508844752</v>
+        <v>36.04202935168417</v>
       </c>
       <c r="I13" t="n">
-        <v>2.304482240826263</v>
+        <v>1.851127386930409</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716434115278197</v>
+        <v>4.677764028641921</v>
       </c>
       <c r="K13" t="n">
-        <v>22.97986095278248</v>
+        <v>15.37089001117287</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69228961838137</v>
+        <v>42.53990433883943</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92326046152336</v>
+        <v>99.93834071040374</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.61904868078985</v>
+        <v>82.63044837756739</v>
       </c>
       <c r="C14" t="n">
-        <v>39.34581193513872</v>
+        <v>40.31662863627347</v>
       </c>
       <c r="D14" t="n">
-        <v>1.509869475085427</v>
+        <v>1.665020235516013</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00555116510702</v>
+        <v>10.98022527818798</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555215974490258</v>
+        <v>0.748908283656343</v>
       </c>
       <c r="G14" t="n">
-        <v>25.12138515365764</v>
+        <v>26.9475791464235</v>
       </c>
       <c r="H14" t="n">
-        <v>36.53902474176872</v>
+        <v>36.06447195709906</v>
       </c>
       <c r="I14" t="n">
-        <v>2.965686563665594</v>
+        <v>1.543566703832356</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722009984056411</v>
+        <v>4.680676772852142</v>
       </c>
       <c r="K14" t="n">
-        <v>16.38095131921015</v>
+        <v>17.36955162243261</v>
       </c>
       <c r="L14" t="n">
-        <v>44.17449725878485</v>
+        <v>42.26239953610143</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90126051313372</v>
+        <v>99.94857979480751</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.72870168780841</v>
+        <v>81.66623468731844</v>
       </c>
       <c r="C15" t="n">
-        <v>38.912591947953</v>
+        <v>39.55996453805993</v>
       </c>
       <c r="D15" t="n">
-        <v>1.476395041880268</v>
+        <v>1.623784821016201</v>
       </c>
       <c r="E15" t="n">
-        <v>12.1529852440322</v>
+        <v>10.92794597006338</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562746861021423</v>
+        <v>0.7493111442921849</v>
       </c>
       <c r="G15" t="n">
-        <v>24.56572426085295</v>
+        <v>26.28020311569022</v>
       </c>
       <c r="H15" t="n">
-        <v>36.57673675007607</v>
+        <v>36.08387213789691</v>
       </c>
       <c r="I15" t="n">
-        <v>2.473868916726393</v>
+        <v>1.317922846533381</v>
       </c>
       <c r="J15" t="n">
-        <v>4.72671678813839</v>
+        <v>4.683194651826154</v>
       </c>
       <c r="K15" t="n">
-        <v>17.27129831219159</v>
+        <v>18.33376531268157</v>
       </c>
       <c r="L15" t="n">
-        <v>43.73372955753137</v>
+        <v>42.0623630067002</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91761981767596</v>
+        <v>99.95609285744172</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.21658602722758</v>
+        <v>79.19402707091524</v>
       </c>
       <c r="C16" t="n">
-        <v>36.78285647738762</v>
+        <v>37.29208227445509</v>
       </c>
       <c r="D16" t="n">
-        <v>1.380474227594904</v>
+        <v>1.521110871336067</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7072979985476</v>
+        <v>10.42008774291476</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569231141258236</v>
+        <v>0.7496576880316135</v>
       </c>
       <c r="G16" t="n">
-        <v>22.9696986662331</v>
+        <v>24.61847292991632</v>
       </c>
       <c r="H16" t="n">
-        <v>36.60809755265139</v>
+        <v>36.10056031887351</v>
       </c>
       <c r="I16" t="n">
-        <v>2.063325004788358</v>
+        <v>1.098776969645383</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730769463286398</v>
+        <v>4.685360550197583</v>
       </c>
       <c r="K16" t="n">
-        <v>19.78341397277241</v>
+        <v>20.80597292908476</v>
       </c>
       <c r="L16" t="n">
-        <v>43.36501096881979</v>
+        <v>41.86533582850088</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93128141897982</v>
+        <v>99.96339103204073</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.91042479379576</v>
+        <v>83.74741219312013</v>
       </c>
       <c r="C17" t="n">
-        <v>38.01592442280618</v>
+        <v>40.34323930212004</v>
       </c>
       <c r="D17" t="n">
-        <v>1.381631206833945</v>
+        <v>1.521813053024541</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49000200783871</v>
+        <v>12.03920280054651</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575574934652478</v>
+        <v>0.7500037482111042</v>
       </c>
       <c r="G17" t="n">
-        <v>23.41859496526675</v>
+        <v>26.05084311854198</v>
       </c>
       <c r="H17" t="n">
-        <v>37.06842423122414</v>
+        <v>37.53823091765462</v>
       </c>
       <c r="I17" t="n">
-        <v>2.059480555009154</v>
+        <v>1.159795128821963</v>
       </c>
       <c r="J17" t="n">
-        <v>4.7347343341578</v>
+        <v>4.6875234263194</v>
       </c>
       <c r="K17" t="n">
-        <v>18.08957520620426</v>
+        <v>16.25258780687988</v>
       </c>
       <c r="L17" t="n">
-        <v>43.82590850618606</v>
+        <v>43.36553089145733</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93140813519649</v>
+        <v>99.96135800045725</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.4352032119405</v>
+        <v>85.29141662506612</v>
       </c>
       <c r="C18" t="n">
-        <v>35.85860305752292</v>
+        <v>41.02311665269528</v>
       </c>
       <c r="D18" t="n">
-        <v>1.290852020107901</v>
+        <v>1.522989579425908</v>
       </c>
       <c r="E18" t="n">
-        <v>11.95559960160468</v>
+        <v>12.59958635725479</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581034658369437</v>
+        <v>0.7505835823826805</v>
       </c>
       <c r="G18" t="n">
-        <v>21.87989129767578</v>
+        <v>26.18167244827738</v>
       </c>
       <c r="H18" t="n">
-        <v>37.09513947814219</v>
+        <v>37.567252037987</v>
       </c>
       <c r="I18" t="n">
-        <v>1.717470687092098</v>
+        <v>1.978185229846615</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738146661480899</v>
+        <v>4.691147389891752</v>
       </c>
       <c r="K18" t="n">
-        <v>20.56479678805949</v>
+        <v>14.70858337493388</v>
       </c>
       <c r="L18" t="n">
-        <v>43.5193923612229</v>
+        <v>44.20241140371287</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94279220680532</v>
+        <v>99.93411143134203</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.42094984120607</v>
+        <v>82.6434663521257</v>
       </c>
       <c r="C19" t="n">
-        <v>35.10873060992033</v>
+        <v>38.68162964299015</v>
       </c>
       <c r="D19" t="n">
-        <v>1.254342476351029</v>
+        <v>1.423877367123753</v>
       </c>
       <c r="E19" t="n">
-        <v>11.85613869348987</v>
+        <v>12.05456870116008</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585649401168625</v>
+        <v>0.75108297699004</v>
       </c>
       <c r="G19" t="n">
-        <v>21.26105595769518</v>
+        <v>24.47783710155275</v>
       </c>
       <c r="H19" t="n">
-        <v>37.1177201067115</v>
+        <v>37.5922470998581</v>
       </c>
       <c r="I19" t="n">
-        <v>1.432096791111249</v>
+        <v>1.649584499253237</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741030875730392</v>
+        <v>4.694268606187748</v>
       </c>
       <c r="K19" t="n">
-        <v>21.57905015879392</v>
+        <v>17.3565336478743</v>
       </c>
       <c r="L19" t="n">
-        <v>43.26451171219984</v>
+        <v>43.9068871194176</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9522924809141</v>
+        <v>99.94505041028205</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.72148726622383</v>
+        <v>79.93453972927452</v>
       </c>
       <c r="C20" t="n">
-        <v>32.62954182476948</v>
+        <v>36.22754848220506</v>
       </c>
       <c r="D20" t="n">
-        <v>1.156436799843527</v>
+        <v>1.323014145175085</v>
       </c>
       <c r="E20" t="n">
-        <v>11.12973381364098</v>
+        <v>11.42989940950069</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589636635125617</v>
+        <v>0.7515137758383493</v>
       </c>
       <c r="G20" t="n">
-        <v>19.60155856679324</v>
+        <v>22.74390019560662</v>
       </c>
       <c r="H20" t="n">
-        <v>37.13723024041116</v>
+        <v>37.61380889429641</v>
       </c>
       <c r="I20" t="n">
-        <v>1.194041285068851</v>
+        <v>1.375442209867682</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743522896953512</v>
+        <v>4.696961098989681</v>
       </c>
       <c r="K20" t="n">
-        <v>24.27851273377616</v>
+        <v>20.06546027072548</v>
       </c>
       <c r="L20" t="n">
-        <v>43.0521649750346</v>
+        <v>43.66116945542355</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96021953358023</v>
+        <v>99.95417820835408</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.73496684409272</v>
+        <v>77.28648146408665</v>
       </c>
       <c r="C21" t="n">
-        <v>36.36427121210784</v>
+        <v>33.79130290119227</v>
       </c>
       <c r="D21" t="n">
-        <v>1.15724714146812</v>
+        <v>1.224922983691513</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14080823759601</v>
+        <v>10.77358980072638</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594954866508268</v>
+        <v>0.7518854719384733</v>
       </c>
       <c r="G21" t="n">
-        <v>21.33220162009081</v>
+        <v>21.05761770574084</v>
       </c>
       <c r="H21" t="n">
-        <v>38.88016093854522</v>
+        <v>37.63241255337269</v>
       </c>
       <c r="I21" t="n">
-        <v>1.718206628174079</v>
+        <v>1.146768749001293</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746846791567669</v>
+        <v>4.699284199615456</v>
       </c>
       <c r="K21" t="n">
-        <v>18.26503315590725</v>
+        <v>22.71351853591336</v>
       </c>
       <c r="L21" t="n">
-        <v>45.31346218249503</v>
+        <v>43.4569718348425</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94276655051013</v>
+        <v>99.96179327194812</v>
       </c>
     </row>
   </sheetData>
